--- a/public/template_skpg.xlsx
+++ b/public/template_skpg.xlsx
@@ -397,91 +397,115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Tahun</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Bulan</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Kecamatan</v>
+      </c>
+      <c r="D1" t="str">
         <v>nama_kelurahan</v>
       </c>
-      <c r="B1" t="str">
+      <c r="E1" t="str">
+        <v>gizi_sangat_kurang</v>
+      </c>
+      <c r="F1" t="str">
         <v>gizi_kurang</v>
       </c>
-      <c r="C1" t="str">
-        <v>gizi_sangat_kurang</v>
-      </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
+        <v>gizi_normal</v>
+      </c>
+      <c r="H1" t="str">
         <v>gizi_berlebih</v>
-      </c>
-      <c r="E1" t="str">
-        <v>gizi_normal</v>
-      </c>
-      <c r="F1" t="str">
-        <v>periode</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Cilegon</v>
+      </c>
+      <c r="D2" t="str">
         <v>Bagendung</v>
       </c>
-      <c r="B2">
+      <c r="E2">
+        <v>72</v>
+      </c>
+      <c r="F2">
         <v>462</v>
       </c>
-      <c r="C2">
-        <v>72</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
+        <v>338</v>
+      </c>
+      <c r="H2">
         <v>8414</v>
-      </c>
-      <c r="E2">
-        <v>338</v>
-      </c>
-      <c r="F2">
-        <v>2025</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Ciwandan</v>
+      </c>
+      <c r="D3" t="str">
         <v>Banjar Negara</v>
       </c>
-      <c r="B3">
+      <c r="E3">
+        <v>92</v>
+      </c>
+      <c r="F3">
         <v>122</v>
       </c>
-      <c r="C3">
-        <v>92</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
+        <v>165</v>
+      </c>
+      <c r="H3">
         <v>7684</v>
-      </c>
-      <c r="E3">
-        <v>165</v>
-      </c>
-      <c r="F3">
-        <v>2025</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Cilegon</v>
+      </c>
+      <c r="D4" t="str">
         <v>Bendungan</v>
       </c>
-      <c r="B4">
+      <c r="E4">
+        <v>98</v>
+      </c>
+      <c r="F4">
         <v>485</v>
       </c>
-      <c r="C4">
-        <v>98</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
+        <v>443</v>
+      </c>
+      <c r="H4">
         <v>6904</v>
-      </c>
-      <c r="E4">
-        <v>443</v>
-      </c>
-      <c r="F4">
-        <v>2025</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H4"/>
   </ignoredErrors>
 </worksheet>
 </file>